--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_20/per_file_predictions_epoch_20.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run1/epoch_20/per_file_predictions_epoch_20.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="522">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,778 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.6575,0.0217,0.0611,0.2169</t>
-  </si>
-  <si>
-    <t>0.0040,0.0505,0.0015,0.9932</t>
-  </si>
-  <si>
-    <t>0.1894,0.0295,0.0010,0.8614</t>
-  </si>
-  <si>
-    <t>0.0348,0.0725,0.0065,0.9639</t>
-  </si>
-  <si>
-    <t>0.9882,0.0117,0.0024,0.0007</t>
-  </si>
-  <si>
-    <t>0.9447,0.0699,0.0097,0.0025</t>
-  </si>
-  <si>
-    <t>0.9742,0.0269,0.0063,0.0015</t>
-  </si>
-  <si>
-    <t>0.9688,0.0276,0.0129,0.0016</t>
-  </si>
-  <si>
-    <t>0.9670,0.0336,0.0094,0.0010</t>
-  </si>
-  <si>
-    <t>0.9793,0.0266,0.0039,0.0009</t>
-  </si>
-  <si>
-    <t>0.9813,0.0151,0.0058,0.0017</t>
-  </si>
-  <si>
-    <t>0.9909,0.0100,0.0015,0.0006</t>
-  </si>
-  <si>
-    <t>0.4893,0.1011,0.4523,0.0172</t>
-  </si>
-  <si>
-    <t>0.2418,0.0300,0.8092,0.0017</t>
-  </si>
-  <si>
-    <t>0.3663,0.0199,0.7634,0.0019</t>
-  </si>
-  <si>
-    <t>0.1011,0.0159,0.8852,0.0189</t>
-  </si>
-  <si>
-    <t>0.6704,0.0470,0.3948,0.0154</t>
-  </si>
-  <si>
-    <t>0.0570,0.9101,0.0544,0.0014</t>
-  </si>
-  <si>
-    <t>0.0677,0.9215,0.0209,0.0009</t>
-  </si>
-  <si>
-    <t>0.3575,0.7177,0.0117,0.0022</t>
-  </si>
-  <si>
-    <t>0.0719,0.8652,0.0674,0.0007</t>
-  </si>
-  <si>
-    <t>0.0226,0.9607,0.0212,0.0002</t>
-  </si>
-  <si>
-    <t>0.1545,0.0071,0.7490,0.0993</t>
-  </si>
-  <si>
-    <t>0.5684,0.0040,0.5094,0.0168</t>
-  </si>
-  <si>
-    <t>0.0131,0.0013,0.9872,0.0026</t>
-  </si>
-  <si>
-    <t>0.0732,0.0233,0.9127,0.0028</t>
-  </si>
-  <si>
-    <t>0.0394,0.0054,0.9688,0.0027</t>
-  </si>
-  <si>
-    <t>0.1399,0.0035,0.8766,0.0182</t>
-  </si>
-  <si>
-    <t>0.0461,0.0069,0.9519,0.0103</t>
-  </si>
-  <si>
-    <t>0.1036,0.8385,0.0994,0.0079</t>
-  </si>
-  <si>
-    <t>0.4156,0.3955,0.2527,0.0118</t>
-  </si>
-  <si>
-    <t>0.0018,0.0225,0.9917,0.0020</t>
-  </si>
-  <si>
-    <t>0.0999,0.5284,0.4998,0.0027</t>
-  </si>
-  <si>
-    <t>0.6770,0.2859,0.0684,0.0116</t>
-  </si>
-  <si>
-    <t>0.4377,0.0840,0.5638,0.0170</t>
-  </si>
-  <si>
-    <t>0.5464,0.5384,0.0164,0.0018</t>
-  </si>
-  <si>
-    <t>0.1012,0.8204,0.1578,0.0038</t>
-  </si>
-  <si>
-    <t>0.1150,0.6327,0.5537,0.0247</t>
-  </si>
-  <si>
-    <t>0.0111,0.0482,0.9464,0.0345</t>
-  </si>
-  <si>
-    <t>0.0586,0.2317,0.8796,0.0121</t>
-  </si>
-  <si>
-    <t>0.0755,0.0013,0.8272,0.0822</t>
-  </si>
-  <si>
-    <t>0.0296,0.0461,0.9423,0.0090</t>
-  </si>
-  <si>
-    <t>0.0125,0.9226,0.2124,0.0024</t>
-  </si>
-  <si>
-    <t>0.0172,0.0075,0.9699,0.0076</t>
-  </si>
-  <si>
-    <t>0.2213,0.6371,0.2476,0.2426</t>
-  </si>
-  <si>
-    <t>0.0144,0.9293,0.0540,0.1488</t>
-  </si>
-  <si>
-    <t>0.0202,0.9449,0.1360,0.0028</t>
-  </si>
-  <si>
-    <t>0.0146,0.9759,0.0171,0.0034</t>
-  </si>
-  <si>
-    <t>0.0056,0.1832,0.9772,0.0008</t>
-  </si>
-  <si>
-    <t>0.0142,0.0505,0.9765,0.0016</t>
-  </si>
-  <si>
-    <t>0.0357,0.0054,0.9696,0.0030</t>
-  </si>
-  <si>
-    <t>0.1201,0.0054,0.9180,0.0053</t>
-  </si>
-  <si>
-    <t>0.0005,0.0012,0.9975,0.0015</t>
-  </si>
-  <si>
-    <t>0.0315,0.0393,0.9532,0.0022</t>
-  </si>
-  <si>
-    <t>0.7927,0.2008,0.0282,0.0008</t>
-  </si>
-  <si>
-    <t>0.9603,0.0291,0.0136,0.0020</t>
-  </si>
-  <si>
-    <t>0.9863,0.0092,0.0022,0.0020</t>
-  </si>
-  <si>
-    <t>0.0074,0.1757,0.9659,0.0005</t>
-  </si>
-  <si>
-    <t>0.9639,0.0380,0.0043,0.0042</t>
-  </si>
-  <si>
-    <t>0.9871,0.0167,0.0012,0.0007</t>
-  </si>
-  <si>
-    <t>0.9491,0.0566,0.0096,0.0017</t>
-  </si>
-  <si>
-    <t>0.0010,0.7502,0.9705,0.0001</t>
-  </si>
-  <si>
-    <t>0.0059,0.0643,0.9801,0.0025</t>
-  </si>
-  <si>
-    <t>0.0100,0.0077,0.9853,0.0018</t>
-  </si>
-  <si>
-    <t>0.0012,0.8405,0.9556,0.0003</t>
-  </si>
-  <si>
-    <t>0.0124,0.0078,0.9833,0.0017</t>
-  </si>
-  <si>
-    <t>0.0276,0.9004,0.1251,0.0015</t>
-  </si>
-  <si>
-    <t>0.0062,0.9807,0.0134,0.0001</t>
-  </si>
-  <si>
-    <t>0.4532,0.0503,0.6361,0.0117</t>
-  </si>
-  <si>
-    <t>0.5750,0.0675,0.5132,0.0085</t>
-  </si>
-  <si>
-    <t>0.0073,0.0263,0.9841,0.0004</t>
-  </si>
-  <si>
-    <t>0.0028,0.7786,0.9141,0.0005</t>
-  </si>
-  <si>
-    <t>0.0060,0.7955,0.8574,0.0005</t>
-  </si>
-  <si>
-    <t>0.0052,0.9559,0.4472,0.0011</t>
-  </si>
-  <si>
-    <t>0.0055,0.8304,0.8096,0.0017</t>
-  </si>
-  <si>
-    <t>0.0066,0.0007,0.0040,0.9901</t>
-  </si>
-  <si>
-    <t>0.0084,0.0032,0.0031,0.9900</t>
-  </si>
-  <si>
-    <t>0.0062,0.0019,0.0014,0.9939</t>
-  </si>
-  <si>
-    <t>0.0233,0.0026,0.0027,0.9772</t>
-  </si>
-  <si>
-    <t>0.0136,0.0051,0.0103,0.9817</t>
-  </si>
-  <si>
-    <t>0.0011,0.0181,0.0011,0.9974</t>
-  </si>
-  <si>
-    <t>0.0038,0.8700,0.8812,0.0007</t>
-  </si>
-  <si>
-    <t>0.0041,0.8033,0.9224,0.0006</t>
-  </si>
-  <si>
-    <t>0.0371,0.5873,0.7914,0.0068</t>
-  </si>
-  <si>
-    <t>0.0033,0.7108,0.9396,0.0007</t>
-  </si>
-  <si>
-    <t>0.0055,0.8897,0.8223,0.0011</t>
-  </si>
-  <si>
-    <t>0.0303,0.2615,0.8981,0.0032</t>
-  </si>
-  <si>
-    <t>0.9603,0.0510,0.0071,0.0018</t>
-  </si>
-  <si>
-    <t>0.9316,0.0739,0.0139,0.0014</t>
-  </si>
-  <si>
-    <t>0.9321,0.0740,0.0100,0.0045</t>
-  </si>
-  <si>
-    <t>0.9885,0.0093,0.0024,0.0012</t>
-  </si>
-  <si>
-    <t>0.9698,0.0274,0.0076,0.0014</t>
-  </si>
-  <si>
-    <t>0.9854,0.0175,0.0020,0.0012</t>
-  </si>
-  <si>
-    <t>0.9829,0.0091,0.0020,0.0045</t>
-  </si>
-  <si>
-    <t>0.9612,0.0426,0.0101,0.0016</t>
-  </si>
-  <si>
-    <t>0.9803,0.0158,0.0031,0.0027</t>
-  </si>
-  <si>
-    <t>0.9835,0.0122,0.0040,0.0015</t>
-  </si>
-  <si>
-    <t>0.9907,0.0074,0.0013,0.0011</t>
-  </si>
-  <si>
-    <t>0.9817,0.0136,0.0048,0.0018</t>
-  </si>
-  <si>
-    <t>0.9822,0.0177,0.0049,0.0007</t>
-  </si>
-  <si>
-    <t>0.9892,0.0106,0.0023,0.0004</t>
-  </si>
-  <si>
-    <t>0.9912,0.0076,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.9896,0.0069,0.0022,0.0014</t>
-  </si>
-  <si>
-    <t>0.0063,0.0133,0.9837,0.0055</t>
-  </si>
-  <si>
-    <t>0.0594,0.0384,0.9204,0.0065</t>
-  </si>
-  <si>
-    <t>0.7142,0.0119,0.2167,0.0528</t>
-  </si>
-  <si>
-    <t>0.1251,0.0053,0.9105,0.0084</t>
-  </si>
-  <si>
-    <t>0.0890,0.8849,0.0351,0.0009</t>
-  </si>
-  <si>
-    <t>0.1435,0.8738,0.0170,0.0022</t>
-  </si>
-  <si>
-    <t>0.2540,0.7799,0.0141,0.0023</t>
-  </si>
-  <si>
-    <t>0.4184,0.6078,0.0364,0.0069</t>
-  </si>
-  <si>
-    <t>0.1717,0.8277,0.0326,0.0025</t>
-  </si>
-  <si>
-    <t>0.0445,0.9329,0.0152,0.0005</t>
-  </si>
-  <si>
-    <t>0.4316,0.5972,0.0203,0.0014</t>
-  </si>
-  <si>
-    <t>0.5036,0.2417,0.2835,0.0146</t>
-  </si>
-  <si>
-    <t>0.1743,0.0044,0.8602,0.0148</t>
-  </si>
-  <si>
-    <t>0.4473,0.2116,0.3246,0.0225</t>
-  </si>
-  <si>
-    <t>0.5158,0.0193,0.6123,0.0120</t>
-  </si>
-  <si>
-    <t>0.1390,0.0820,0.0901,0.8236</t>
-  </si>
-  <si>
-    <t>0.0399,0.9337,0.0583,0.0072</t>
-  </si>
-  <si>
-    <t>0.0328,0.8849,0.2172,0.0911</t>
-  </si>
-  <si>
-    <t>0.1209,0.7739,0.1434,0.1364</t>
-  </si>
-  <si>
-    <t>0.0071,0.9667,0.2504,0.0011</t>
-  </si>
-  <si>
-    <t>0.0468,0.8884,0.1214,0.0012</t>
-  </si>
-  <si>
-    <t>0.3102,0.6787,0.0438,0.0016</t>
-  </si>
-  <si>
-    <t>0.5180,0.4917,0.0394,0.0019</t>
-  </si>
-  <si>
-    <t>0.7996,0.1577,0.1003,0.0083</t>
-  </si>
-  <si>
-    <t>0.9830,0.0149,0.0038,0.0014</t>
-  </si>
-  <si>
-    <t>0.9835,0.0074,0.0032,0.0038</t>
-  </si>
-  <si>
-    <t>0.9761,0.0248,0.0034,0.0019</t>
-  </si>
-  <si>
-    <t>0.9855,0.0067,0.0007,0.0043</t>
-  </si>
-  <si>
-    <t>0.8529,0.1128,0.0550,0.0048</t>
-  </si>
-  <si>
-    <t>0.9525,0.0368,0.0159,0.0032</t>
-  </si>
-  <si>
-    <t>0.9865,0.0050,0.0030,0.0034</t>
-  </si>
-  <si>
-    <t>0.0061,0.4323,0.9550,0.0008</t>
-  </si>
-  <si>
-    <t>0.0108,0.5222,0.9127,0.0006</t>
-  </si>
-  <si>
-    <t>0.0196,0.2665,0.9381,0.0050</t>
-  </si>
-  <si>
-    <t>0.0136,0.0239,0.9786,0.0005</t>
-  </si>
-  <si>
-    <t>0.3124,0.0696,0.1904,0.5178</t>
-  </si>
-  <si>
-    <t>0.6284,0.1243,0.2345,0.0654</t>
-  </si>
-  <si>
-    <t>0.1632,0.0043,0.9289,0.0015</t>
-  </si>
-  <si>
-    <t>0.7233,0.0302,0.3063,0.0147</t>
-  </si>
-  <si>
-    <t>0.0248,0.0049,0.0024,0.9824</t>
-  </si>
-  <si>
-    <t>0.0006,0.0019,0.0003,0.9989</t>
-  </si>
-  <si>
-    <t>0.0053,0.0031,0.0027,0.9927</t>
-  </si>
-  <si>
-    <t>0.0139,0.0041,0.0010,0.9900</t>
-  </si>
-  <si>
-    <t>0.0012,0.9128,0.8973,0.0006</t>
-  </si>
-  <si>
-    <t>0.9273,0.0720,0.0095,0.0032</t>
-  </si>
-  <si>
-    <t>0.2275,0.8044,0.0078,0.0124</t>
-  </si>
-  <si>
-    <t>0.9766,0.0201,0.0022,0.0029</t>
-  </si>
-  <si>
-    <t>0.6900,0.3721,0.0154,0.0015</t>
-  </si>
-  <si>
-    <t>0.9511,0.0130,0.0017,0.0293</t>
-  </si>
-  <si>
-    <t>0.5912,0.0458,0.0609,0.3524</t>
-  </si>
-  <si>
-    <t>0.9517,0.0269,0.0137,0.0059</t>
-  </si>
-  <si>
-    <t>0.0744,0.0377,0.8816,0.0556</t>
-  </si>
-  <si>
-    <t>0.2662,0.0070,0.0112,0.8106</t>
-  </si>
-  <si>
-    <t>0.8449,0.0521,0.0910,0.0341</t>
-  </si>
-  <si>
-    <t>0.2555,0.7498,0.0332,0.0148</t>
-  </si>
-  <si>
-    <t>0.6937,0.3271,0.0256,0.0102</t>
-  </si>
-  <si>
-    <t>0.4756,0.3395,0.2175,0.0113</t>
-  </si>
-  <si>
-    <t>0.5320,0.1962,0.2675,0.0378</t>
-  </si>
-  <si>
-    <t>0.4458,0.3856,0.1616,0.0045</t>
-  </si>
-  <si>
-    <t>0.5662,0.4011,0.0673,0.0200</t>
-  </si>
-  <si>
-    <t>0.9822,0.0136,0.0032,0.0024</t>
-  </si>
-  <si>
-    <t>0.9877,0.0133,0.0009,0.0011</t>
-  </si>
-  <si>
-    <t>0.9867,0.0063,0.0038,0.0019</t>
-  </si>
-  <si>
-    <t>0.9790,0.0121,0.0052,0.0036</t>
-  </si>
-  <si>
-    <t>0.9802,0.0137,0.0055,0.0012</t>
-  </si>
-  <si>
-    <t>0.9703,0.0218,0.0102,0.0025</t>
-  </si>
-  <si>
-    <t>0.9690,0.0207,0.0077,0.0031</t>
-  </si>
-  <si>
-    <t>0.9556,0.0350,0.0094,0.0045</t>
-  </si>
-  <si>
-    <t>0.3461,0.6824,0.0415,0.0043</t>
-  </si>
-  <si>
-    <t>0.5477,0.4363,0.0431,0.0021</t>
-  </si>
-  <si>
-    <t>0.4936,0.4976,0.0387,0.0018</t>
-  </si>
-  <si>
-    <t>0.6244,0.2121,0.2772,0.0132</t>
-  </si>
-  <si>
-    <t>0.8930,0.1617,0.0060,0.0014</t>
-  </si>
-  <si>
-    <t>0.8460,0.0604,0.1521,0.0057</t>
-  </si>
-  <si>
-    <t>0.9063,0.0966,0.0180,0.0025</t>
-  </si>
-  <si>
-    <t>0.4391,0.4935,0.0556,0.0018</t>
-  </si>
-  <si>
-    <t>0.0009,0.0292,0.9966,0.0000</t>
-  </si>
-  <si>
-    <t>0.8734,0.0713,0.0862,0.0033</t>
-  </si>
-  <si>
-    <t>0.0027,0.0029,0.9941,0.0009</t>
-  </si>
-  <si>
-    <t>0.0014,0.0657,0.9926,0.0005</t>
-  </si>
-  <si>
-    <t>0.0626,0.0077,0.9476,0.0064</t>
-  </si>
-  <si>
-    <t>0.0073,0.0467,0.9806,0.0012</t>
-  </si>
-  <si>
-    <t>0.0026,0.0041,0.9944,0.0003</t>
-  </si>
-  <si>
-    <t>0.0059,0.0011,0.9903,0.0047</t>
-  </si>
-  <si>
-    <t>0.0018,0.0010,0.9959,0.0014</t>
-  </si>
-  <si>
-    <t>0.4731,0.1397,0.4144,0.0527</t>
-  </si>
-  <si>
-    <t>0.4048,0.0216,0.7502,0.0018</t>
-  </si>
-  <si>
-    <t>0.5574,0.0547,0.4633,0.0233</t>
-  </si>
-  <si>
-    <t>0.1604,0.1939,0.6793,0.0042</t>
-  </si>
-  <si>
-    <t>0.1618,0.1797,0.6375,0.0129</t>
-  </si>
-  <si>
-    <t>0.6678,0.0106,0.5274,0.0056</t>
-  </si>
-  <si>
-    <t>0.6103,0.0910,0.3706,0.0181</t>
-  </si>
-  <si>
-    <t>0.4295,0.0601,0.6061,0.0167</t>
-  </si>
-  <si>
-    <t>0.6733,0.4038,0.0126,0.0012</t>
-  </si>
-  <si>
-    <t>0.8409,0.2297,0.0066,0.0010</t>
-  </si>
-  <si>
-    <t>0.2939,0.5518,0.1124,0.0009</t>
-  </si>
-  <si>
-    <t>0.7960,0.2315,0.0284,0.0028</t>
-  </si>
-  <si>
-    <t>0.6637,0.4011,0.0186,0.0021</t>
-  </si>
-  <si>
-    <t>0.5304,0.0561,0.5048,0.0158</t>
-  </si>
-  <si>
-    <t>0.5150,0.0067,0.6717,0.0081</t>
-  </si>
-  <si>
-    <t>0.5865,0.0062,0.1642,0.1370</t>
-  </si>
-  <si>
-    <t>0.5296,0.0291,0.4886,0.0301</t>
-  </si>
-  <si>
-    <t>0.8379,0.0074,0.1047,0.0344</t>
-  </si>
-  <si>
-    <t>0.2149,0.0841,0.7027,0.0410</t>
-  </si>
-  <si>
-    <t>0.1202,0.0710,0.8305,0.0350</t>
-  </si>
-  <si>
-    <t>0.0083,0.7403,0.9050,0.0036</t>
-  </si>
-  <si>
-    <t>0.0303,0.1350,0.9493,0.0035</t>
-  </si>
-  <si>
-    <t>0.0182,0.2430,0.9432,0.0064</t>
-  </si>
-  <si>
-    <t>0.9868,0.0108,0.0018,0.0017</t>
-  </si>
-  <si>
-    <t>0.9810,0.0147,0.0060,0.0008</t>
-  </si>
-  <si>
-    <t>0.9694,0.0346,0.0066,0.0022</t>
-  </si>
-  <si>
-    <t>0.9784,0.0209,0.0060,0.0014</t>
-  </si>
-  <si>
-    <t>0.9842,0.0137,0.0020,0.0019</t>
-  </si>
-  <si>
-    <t>0.9741,0.0227,0.0073,0.0023</t>
-  </si>
-  <si>
-    <t>0.9768,0.0187,0.0040,0.0030</t>
-  </si>
-  <si>
-    <t>0.9716,0.0208,0.0111,0.0022</t>
-  </si>
-  <si>
-    <t>0.0373,0.0388,0.9458,0.0020</t>
-  </si>
-  <si>
-    <t>0.4684,0.3490,0.2118,0.0256</t>
-  </si>
-  <si>
-    <t>0.7998,0.0718,0.2015,0.0151</t>
-  </si>
-  <si>
-    <t>0.0026,0.0091,0.9924,0.0008</t>
-  </si>
-  <si>
-    <t>0.0003,0.0004,0.9982,0.0024</t>
-  </si>
-  <si>
-    <t>0.0095,0.2572,0.9389,0.0015</t>
-  </si>
-  <si>
-    <t>0.0023,0.0060,0.9951,0.0006</t>
-  </si>
-  <si>
-    <t>0.0462,0.0255,0.9344,0.0071</t>
-  </si>
-  <si>
-    <t>0.0048,0.0361,0.9906,0.0007</t>
-  </si>
-  <si>
-    <t>0.0094,0.0033,0.9872,0.0013</t>
-  </si>
-  <si>
-    <t>0.4670,0.0487,0.5557,0.0259</t>
-  </si>
-  <si>
-    <t>0.5167,0.0026,0.6462,0.0090</t>
-  </si>
-  <si>
-    <t>0.5117,0.0043,0.5945,0.0160</t>
-  </si>
-  <si>
-    <t>0.8894,0.0021,0.1281,0.0093</t>
-  </si>
-  <si>
-    <t>0.9636,0.0631,0.0022,0.0010</t>
-  </si>
-  <si>
-    <t>0.9029,0.1347,0.0065,0.0007</t>
-  </si>
-  <si>
-    <t>0.9826,0.0184,0.0038,0.0008</t>
-  </si>
-  <si>
-    <t>0.9732,0.0272,0.0052,0.0012</t>
-  </si>
-  <si>
-    <t>0.9384,0.0563,0.0191,0.0037</t>
-  </si>
-  <si>
-    <t>0.9439,0.0373,0.0275,0.0017</t>
-  </si>
-  <si>
-    <t>0.9758,0.0333,0.0029,0.0009</t>
-  </si>
-  <si>
-    <t>0.9235,0.0978,0.0097,0.0029</t>
-  </si>
-  <si>
-    <t>0.0345,0.0775,0.9038,0.0267</t>
-  </si>
-  <si>
-    <t>0.0010,0.0247,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0239,0.0320,0.9711,0.0007</t>
-  </si>
-  <si>
-    <t>0.0780,0.0984,0.8611,0.0108</t>
-  </si>
-  <si>
-    <t>0.0109,0.0081,0.9869,0.0008</t>
-  </si>
-  <si>
-    <t>0.0379,0.0097,0.9312,0.0459</t>
-  </si>
-  <si>
-    <t>0.2894,0.0484,0.6893,0.0602</t>
-  </si>
-  <si>
-    <t>0.0585,0.2798,0.7792,0.1024</t>
-  </si>
-  <si>
-    <t>0.3233,0.0122,0.0144,0.6810</t>
-  </si>
-  <si>
-    <t>0.0090,0.0143,0.0016,0.9922</t>
-  </si>
-  <si>
-    <t>0.0131,0.0047,0.0011,0.9899</t>
-  </si>
-  <si>
-    <t>0.0017,0.0029,0.0003,0.9983</t>
-  </si>
-  <si>
-    <t>0.0022,0.0025,0.0001,0.9982</t>
-  </si>
-  <si>
-    <t>0.4824,0.0595,0.0130,0.5164</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.8185,0.0837,0.0441,0.0677</t>
+  </si>
+  <si>
+    <t>0.0103,0.0025,0.0004,0.9934</t>
+  </si>
+  <si>
+    <t>0.8197,0.0184,0.0308,0.1205</t>
+  </si>
+  <si>
+    <t>0.1177,0.0103,0.0015,0.9429</t>
+  </si>
+  <si>
+    <t>0.9806,0.0215,0.0049,0.0007</t>
+  </si>
+  <si>
+    <t>0.9893,0.0085,0.0015,0.0011</t>
+  </si>
+  <si>
+    <t>0.9524,0.0515,0.0083,0.0027</t>
+  </si>
+  <si>
+    <t>0.9887,0.0104,0.0014,0.0013</t>
+  </si>
+  <si>
+    <t>0.9530,0.0521,0.0143,0.0029</t>
+  </si>
+  <si>
+    <t>0.9870,0.0164,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.9883,0.0112,0.0030,0.0006</t>
+  </si>
+  <si>
+    <t>0.9908,0.0055,0.0026,0.0009</t>
+  </si>
+  <si>
+    <t>0.4785,0.1392,0.4200,0.0218</t>
+  </si>
+  <si>
+    <t>0.3286,0.0171,0.8064,0.0018</t>
+  </si>
+  <si>
+    <t>0.3073,0.0096,0.8297,0.0043</t>
+  </si>
+  <si>
+    <t>0.0895,0.0104,0.9259,0.0049</t>
+  </si>
+  <si>
+    <t>0.5359,0.0126,0.6472,0.0094</t>
+  </si>
+  <si>
+    <t>0.0478,0.9424,0.0233,0.0009</t>
+  </si>
+  <si>
+    <t>0.1465,0.8420,0.0502,0.0015</t>
+  </si>
+  <si>
+    <t>0.5770,0.5060,0.0147,0.0072</t>
+  </si>
+  <si>
+    <t>0.0308,0.9509,0.0206,0.0004</t>
+  </si>
+  <si>
+    <t>0.0304,0.9612,0.0133,0.0004</t>
+  </si>
+  <si>
+    <t>0.4740,0.0073,0.6489,0.0135</t>
+  </si>
+  <si>
+    <t>0.3429,0.0021,0.6394,0.0262</t>
+  </si>
+  <si>
+    <t>0.0051,0.0017,0.9933,0.0010</t>
+  </si>
+  <si>
+    <t>0.1564,0.0102,0.8872,0.0060</t>
+  </si>
+  <si>
+    <t>0.0791,0.0054,0.9358,0.0093</t>
+  </si>
+  <si>
+    <t>0.1271,0.0261,0.8978,0.0030</t>
+  </si>
+  <si>
+    <t>0.0014,0.0005,0.9916,0.0165</t>
+  </si>
+  <si>
+    <t>0.2755,0.6819,0.0821,0.0069</t>
+  </si>
+  <si>
+    <t>0.5186,0.3652,0.1454,0.0090</t>
+  </si>
+  <si>
+    <t>0.0020,0.0117,0.9923,0.0019</t>
+  </si>
+  <si>
+    <t>0.0429,0.6663,0.5130,0.0038</t>
+  </si>
+  <si>
+    <t>0.7096,0.2471,0.0901,0.0174</t>
+  </si>
+  <si>
+    <t>0.2319,0.1557,0.6486,0.0061</t>
+  </si>
+  <si>
+    <t>0.3770,0.6882,0.0145,0.0027</t>
+  </si>
+  <si>
+    <t>0.1155,0.8175,0.1184,0.0040</t>
+  </si>
+  <si>
+    <t>0.0298,0.7043,0.7803,0.0077</t>
+  </si>
+  <si>
+    <t>0.0117,0.3560,0.9503,0.0053</t>
+  </si>
+  <si>
+    <t>0.0692,0.2229,0.8812,0.0131</t>
+  </si>
+  <si>
+    <t>0.2855,0.0022,0.6219,0.0484</t>
+  </si>
+  <si>
+    <t>0.0410,0.0232,0.9534,0.0018</t>
+  </si>
+  <si>
+    <t>0.0300,0.8742,0.2726,0.0051</t>
+  </si>
+  <si>
+    <t>0.0249,0.0457,0.9408,0.0127</t>
+  </si>
+  <si>
+    <t>0.0274,0.2891,0.0244,0.9353</t>
+  </si>
+  <si>
+    <t>0.0058,0.9623,0.0276,0.1088</t>
+  </si>
+  <si>
+    <t>0.0060,0.9781,0.0425,0.0042</t>
+  </si>
+  <si>
+    <t>0.0222,0.9517,0.0678,0.0164</t>
+  </si>
+  <si>
+    <t>0.0294,0.0186,0.9716,0.0019</t>
+  </si>
+  <si>
+    <t>0.0007,0.1751,0.9923,0.0001</t>
+  </si>
+  <si>
+    <t>0.1347,0.0111,0.8883,0.0149</t>
+  </si>
+  <si>
+    <t>0.0134,0.0015,0.9878,0.0018</t>
+  </si>
+  <si>
+    <t>0.0111,0.0099,0.9786,0.0062</t>
+  </si>
+  <si>
+    <t>0.0054,0.0120,0.9850,0.0016</t>
+  </si>
+  <si>
+    <t>0.7550,0.2361,0.0392,0.0023</t>
+  </si>
+  <si>
+    <t>0.9679,0.0245,0.0095,0.0022</t>
+  </si>
+  <si>
+    <t>0.9573,0.0397,0.0051,0.0029</t>
+  </si>
+  <si>
+    <t>0.0021,0.0100,0.9948,0.0008</t>
+  </si>
+  <si>
+    <t>0.9495,0.0435,0.0184,0.0027</t>
+  </si>
+  <si>
+    <t>0.9892,0.0134,0.0014,0.0007</t>
+  </si>
+  <si>
+    <t>0.9576,0.0633,0.0049,0.0005</t>
+  </si>
+  <si>
+    <t>0.0063,0.8574,0.8347,0.0041</t>
+  </si>
+  <si>
+    <t>0.0089,0.0530,0.9812,0.0011</t>
+  </si>
+  <si>
+    <t>0.0111,0.1760,0.9517,0.0103</t>
+  </si>
+  <si>
+    <t>0.0046,0.8204,0.8917,0.0004</t>
+  </si>
+  <si>
+    <t>0.0036,0.0014,0.9948,0.0014</t>
+  </si>
+  <si>
+    <t>0.0493,0.8715,0.1271,0.0013</t>
+  </si>
+  <si>
+    <t>0.0190,0.9656,0.0056,0.0007</t>
+  </si>
+  <si>
+    <t>0.6060,0.0424,0.5330,0.0184</t>
+  </si>
+  <si>
+    <t>0.6299,0.0495,0.4133,0.0237</t>
+  </si>
+  <si>
+    <t>0.0111,0.0535,0.9763,0.0017</t>
+  </si>
+  <si>
+    <t>0.0032,0.7779,0.8918,0.0005</t>
+  </si>
+  <si>
+    <t>0.0266,0.2565,0.8974,0.0009</t>
+  </si>
+  <si>
+    <t>0.0019,0.9279,0.7866,0.0021</t>
+  </si>
+  <si>
+    <t>0.0026,0.8979,0.8136,0.0006</t>
+  </si>
+  <si>
+    <t>0.0071,0.0014,0.0009,0.9936</t>
+  </si>
+  <si>
+    <t>0.0024,0.0027,0.0004,0.9974</t>
+  </si>
+  <si>
+    <t>0.0073,0.0211,0.0055,0.9885</t>
+  </si>
+  <si>
+    <t>0.0051,0.0031,0.0015,0.9946</t>
+  </si>
+  <si>
+    <t>0.0226,0.0060,0.0018,0.9849</t>
+  </si>
+  <si>
+    <t>0.0016,0.0018,0.0008,0.9980</t>
+  </si>
+  <si>
+    <t>0.0045,0.8236,0.8999,0.0015</t>
+  </si>
+  <si>
+    <t>0.0048,0.7471,0.9095,0.0009</t>
+  </si>
+  <si>
+    <t>0.0116,0.4470,0.8777,0.0015</t>
+  </si>
+  <si>
+    <t>0.0163,0.6033,0.8590,0.0039</t>
+  </si>
+  <si>
+    <t>0.0025,0.8585,0.9052,0.0003</t>
+  </si>
+  <si>
+    <t>0.0190,0.5239,0.8714,0.0023</t>
+  </si>
+  <si>
+    <t>0.9109,0.0603,0.0507,0.0008</t>
+  </si>
+  <si>
+    <t>0.9667,0.0439,0.0039,0.0007</t>
+  </si>
+  <si>
+    <t>0.9551,0.0625,0.0041,0.0009</t>
+  </si>
+  <si>
+    <t>0.9767,0.0330,0.0017,0.0014</t>
+  </si>
+  <si>
+    <t>0.9698,0.0259,0.0064,0.0033</t>
+  </si>
+  <si>
+    <t>0.9778,0.0244,0.0036,0.0020</t>
+  </si>
+  <si>
+    <t>0.9557,0.0656,0.0034,0.0026</t>
+  </si>
+  <si>
+    <t>0.9813,0.0161,0.0039,0.0015</t>
+  </si>
+  <si>
+    <t>0.9905,0.0100,0.0013,0.0007</t>
+  </si>
+  <si>
+    <t>0.9907,0.0088,0.0018,0.0006</t>
+  </si>
+  <si>
+    <t>0.9944,0.0030,0.0005,0.0009</t>
+  </si>
+  <si>
+    <t>0.9885,0.0077,0.0030,0.0014</t>
+  </si>
+  <si>
+    <t>0.9897,0.0108,0.0021,0.0004</t>
+  </si>
+  <si>
+    <t>0.9701,0.0318,0.0068,0.0017</t>
+  </si>
+  <si>
+    <t>0.9930,0.0044,0.0007,0.0012</t>
+  </si>
+  <si>
+    <t>0.9754,0.0345,0.0025,0.0009</t>
+  </si>
+  <si>
+    <t>0.0006,0.0015,0.9978,0.0016</t>
+  </si>
+  <si>
+    <t>0.0356,0.0192,0.9590,0.0034</t>
+  </si>
+  <si>
+    <t>0.7313,0.0104,0.3648,0.0135</t>
+  </si>
+  <si>
+    <t>0.0597,0.0213,0.9164,0.0139</t>
+  </si>
+  <si>
+    <t>0.1132,0.8911,0.0209,0.0012</t>
+  </si>
+  <si>
+    <t>0.0944,0.8971,0.0316,0.0012</t>
+  </si>
+  <si>
+    <t>0.1391,0.8916,0.0091,0.0020</t>
+  </si>
+  <si>
+    <t>0.5023,0.5767,0.0117,0.0021</t>
+  </si>
+  <si>
+    <t>0.0996,0.8610,0.0441,0.0016</t>
+  </si>
+  <si>
+    <t>0.0826,0.9013,0.0180,0.0005</t>
+  </si>
+  <si>
+    <t>0.8260,0.2285,0.0112,0.0013</t>
+  </si>
+  <si>
+    <t>0.6694,0.0670,0.2989,0.0245</t>
+  </si>
+  <si>
+    <t>0.2632,0.0219,0.7894,0.0117</t>
+  </si>
+  <si>
+    <t>0.5609,0.1061,0.3570,0.0387</t>
+  </si>
+  <si>
+    <t>0.5534,0.0308,0.5180,0.0197</t>
+  </si>
+  <si>
+    <t>0.6234,0.1561,0.1969,0.1097</t>
+  </si>
+  <si>
+    <t>0.0164,0.9685,0.0386,0.0015</t>
+  </si>
+  <si>
+    <t>0.0100,0.9591,0.0636,0.0384</t>
+  </si>
+  <si>
+    <t>0.3104,0.6500,0.0534,0.0719</t>
+  </si>
+  <si>
+    <t>0.0039,0.9740,0.2219,0.0022</t>
+  </si>
+  <si>
+    <t>0.0495,0.9036,0.0936,0.0013</t>
+  </si>
+  <si>
+    <t>0.5477,0.4393,0.0499,0.0024</t>
+  </si>
+  <si>
+    <t>0.1583,0.8338,0.0316,0.0018</t>
+  </si>
+  <si>
+    <t>0.9465,0.0487,0.0103,0.0039</t>
+  </si>
+  <si>
+    <t>0.9854,0.0121,0.0024,0.0010</t>
+  </si>
+  <si>
+    <t>0.9888,0.0087,0.0008,0.0021</t>
+  </si>
+  <si>
+    <t>0.9294,0.0676,0.0176,0.0044</t>
+  </si>
+  <si>
+    <t>0.9819,0.0170,0.0052,0.0009</t>
+  </si>
+  <si>
+    <t>0.9499,0.0278,0.0188,0.0070</t>
+  </si>
+  <si>
+    <t>0.9389,0.0757,0.0092,0.0031</t>
+  </si>
+  <si>
+    <t>0.9512,0.0346,0.0195,0.0030</t>
+  </si>
+  <si>
+    <t>0.0047,0.7555,0.9014,0.0013</t>
+  </si>
+  <si>
+    <t>0.0044,0.3274,0.9575,0.0004</t>
+  </si>
+  <si>
+    <t>0.0250,0.6257,0.8131,0.0049</t>
+  </si>
+  <si>
+    <t>0.0295,0.0402,0.9584,0.0013</t>
+  </si>
+  <si>
+    <t>0.4604,0.1100,0.4990,0.0783</t>
+  </si>
+  <si>
+    <t>0.7717,0.0121,0.2699,0.0192</t>
+  </si>
+  <si>
+    <t>0.4203,0.0049,0.7635,0.0068</t>
+  </si>
+  <si>
+    <t>0.3442,0.3738,0.2227,0.0082</t>
+  </si>
+  <si>
+    <t>0.0843,0.0035,0.0087,0.9327</t>
+  </si>
+  <si>
+    <t>0.0003,0.0015,0.0007,0.9990</t>
+  </si>
+  <si>
+    <t>0.0005,0.0015,0.0009,0.9987</t>
+  </si>
+  <si>
+    <t>0.0189,0.0036,0.0091,0.9794</t>
+  </si>
+  <si>
+    <t>0.0053,0.7974,0.8987,0.0018</t>
+  </si>
+  <si>
+    <t>0.9760,0.0249,0.0035,0.0012</t>
+  </si>
+  <si>
+    <t>0.5220,0.4520,0.0641,0.0098</t>
+  </si>
+  <si>
+    <t>0.9738,0.0122,0.0058,0.0041</t>
+  </si>
+  <si>
+    <t>0.9035,0.1018,0.0174,0.0024</t>
+  </si>
+  <si>
+    <t>0.9131,0.0165,0.0502,0.0251</t>
+  </si>
+  <si>
+    <t>0.3910,0.0516,0.1172,0.5300</t>
+  </si>
+  <si>
+    <t>0.9574,0.0401,0.0063,0.0017</t>
+  </si>
+  <si>
+    <t>0.0457,0.0235,0.9335,0.0207</t>
+  </si>
+  <si>
+    <t>0.7360,0.0032,0.0211,0.1662</t>
+  </si>
+  <si>
+    <t>0.9363,0.0345,0.0071,0.0143</t>
+  </si>
+  <si>
+    <t>0.7440,0.1375,0.1253,0.0164</t>
+  </si>
+  <si>
+    <t>0.7243,0.2508,0.0408,0.0075</t>
+  </si>
+  <si>
+    <t>0.3218,0.6790,0.0629,0.0085</t>
+  </si>
+  <si>
+    <t>0.6944,0.0972,0.2137,0.0238</t>
+  </si>
+  <si>
+    <t>0.7030,0.1734,0.1238,0.0071</t>
+  </si>
+  <si>
+    <t>0.6209,0.3345,0.0899,0.0348</t>
+  </si>
+  <si>
+    <t>0.9628,0.0353,0.0105,0.0024</t>
+  </si>
+  <si>
+    <t>0.9495,0.0566,0.0076,0.0048</t>
+  </si>
+  <si>
+    <t>0.9855,0.0149,0.0039,0.0007</t>
+  </si>
+  <si>
+    <t>0.9455,0.0352,0.0235,0.0044</t>
+  </si>
+  <si>
+    <t>0.9396,0.0649,0.0155,0.0038</t>
+  </si>
+  <si>
+    <t>0.9871,0.0131,0.0017,0.0010</t>
+  </si>
+  <si>
+    <t>0.9846,0.0096,0.0049,0.0015</t>
+  </si>
+  <si>
+    <t>0.9874,0.0083,0.0017,0.0016</t>
+  </si>
+  <si>
+    <t>0.2791,0.6998,0.0515,0.0020</t>
+  </si>
+  <si>
+    <t>0.6358,0.4317,0.0133,0.0009</t>
+  </si>
+  <si>
+    <t>0.3469,0.6919,0.0167,0.0021</t>
+  </si>
+  <si>
+    <t>0.3209,0.1774,0.5567,0.0023</t>
+  </si>
+  <si>
+    <t>0.9071,0.1184,0.0111,0.0024</t>
+  </si>
+  <si>
+    <t>0.8443,0.1077,0.0825,0.0053</t>
+  </si>
+  <si>
+    <t>0.9438,0.0810,0.0042,0.0017</t>
+  </si>
+  <si>
+    <t>0.8178,0.1762,0.0364,0.0057</t>
+  </si>
+  <si>
+    <t>0.0027,0.0172,0.9949,0.0001</t>
+  </si>
+  <si>
+    <t>0.9498,0.0279,0.0245,0.0041</t>
+  </si>
+  <si>
+    <t>0.0008,0.0008,0.9968,0.0033</t>
+  </si>
+  <si>
+    <t>0.0024,0.0269,0.9918,0.0011</t>
+  </si>
+  <si>
+    <t>0.0219,0.0047,0.9809,0.0018</t>
+  </si>
+  <si>
+    <t>0.0023,0.0437,0.9924,0.0002</t>
+  </si>
+  <si>
+    <t>0.0175,0.0060,0.9802,0.0018</t>
+  </si>
+  <si>
+    <t>0.0022,0.0030,0.9961,0.0004</t>
+  </si>
+  <si>
+    <t>0.0104,0.0027,0.9908,0.0004</t>
+  </si>
+  <si>
+    <t>0.1516,0.0150,0.8975,0.0014</t>
+  </si>
+  <si>
+    <t>0.2393,0.0122,0.8353,0.0053</t>
+  </si>
+  <si>
+    <t>0.4442,0.0825,0.5666,0.0081</t>
+  </si>
+  <si>
+    <t>0.2807,0.1485,0.5450,0.0059</t>
+  </si>
+  <si>
+    <t>0.3380,0.0572,0.6664,0.0044</t>
+  </si>
+  <si>
+    <t>0.4697,0.1070,0.4426,0.0101</t>
+  </si>
+  <si>
+    <t>0.4262,0.0369,0.6308,0.0131</t>
+  </si>
+  <si>
+    <t>0.4472,0.0156,0.7073,0.0071</t>
+  </si>
+  <si>
+    <t>0.7548,0.3129,0.0158,0.0013</t>
+  </si>
+  <si>
+    <t>0.6808,0.3463,0.0170,0.0012</t>
+  </si>
+  <si>
+    <t>0.4638,0.5474,0.0272,0.0011</t>
+  </si>
+  <si>
+    <t>0.9052,0.1271,0.0110,0.0017</t>
+  </si>
+  <si>
+    <t>0.8566,0.2170,0.0081,0.0018</t>
+  </si>
+  <si>
+    <t>0.8020,0.0120,0.1590,0.0274</t>
+  </si>
+  <si>
+    <t>0.6364,0.0116,0.3805,0.0291</t>
+  </si>
+  <si>
+    <t>0.5572,0.0141,0.0370,0.4351</t>
+  </si>
+  <si>
+    <t>0.6830,0.0089,0.2578,0.0465</t>
+  </si>
+  <si>
+    <t>0.7918,0.0451,0.1356,0.0448</t>
+  </si>
+  <si>
+    <t>0.0757,0.0428,0.8807,0.0249</t>
+  </si>
+  <si>
+    <t>0.0455,0.0866,0.9354,0.0046</t>
+  </si>
+  <si>
+    <t>0.0077,0.0489,0.9794,0.0025</t>
+  </si>
+  <si>
+    <t>0.0702,0.0037,0.9161,0.0230</t>
+  </si>
+  <si>
+    <t>0.0273,0.1081,0.9391,0.0032</t>
+  </si>
+  <si>
+    <t>0.9693,0.0346,0.0040,0.0028</t>
+  </si>
+  <si>
+    <t>0.9771,0.0308,0.0028,0.0014</t>
+  </si>
+  <si>
+    <t>0.9731,0.0393,0.0025,0.0015</t>
+  </si>
+  <si>
+    <t>0.9099,0.0657,0.0320,0.0008</t>
+  </si>
+  <si>
+    <t>0.9822,0.0176,0.0021,0.0019</t>
+  </si>
+  <si>
+    <t>0.9809,0.0181,0.0033,0.0019</t>
+  </si>
+  <si>
+    <t>0.9623,0.0309,0.0065,0.0051</t>
+  </si>
+  <si>
+    <t>0.9766,0.0226,0.0032,0.0030</t>
+  </si>
+  <si>
+    <t>0.1656,0.1386,0.7607,0.0065</t>
+  </si>
+  <si>
+    <t>0.3103,0.3645,0.3528,0.0123</t>
+  </si>
+  <si>
+    <t>0.7331,0.1062,0.1843,0.0134</t>
+  </si>
+  <si>
+    <t>0.0031,0.0038,0.9946,0.0004</t>
+  </si>
+  <si>
+    <t>0.0008,0.0069,0.9940,0.0028</t>
+  </si>
+  <si>
+    <t>0.0501,0.0342,0.9323,0.0051</t>
+  </si>
+  <si>
+    <t>0.0005,0.0014,0.9985,0.0006</t>
+  </si>
+  <si>
+    <t>0.0522,0.0053,0.9585,0.0030</t>
+  </si>
+  <si>
+    <t>0.0070,0.0163,0.9912,0.0004</t>
+  </si>
+  <si>
+    <t>0.0161,0.0224,0.9678,0.0027</t>
+  </si>
+  <si>
+    <t>0.0788,0.0130,0.9300,0.0051</t>
+  </si>
+  <si>
+    <t>0.7112,0.0040,0.3796,0.0133</t>
+  </si>
+  <si>
+    <t>0.4995,0.0290,0.6124,0.0075</t>
+  </si>
+  <si>
+    <t>0.7210,0.0151,0.1972,0.0563</t>
+  </si>
+  <si>
+    <t>0.9802,0.0168,0.0042,0.0023</t>
+  </si>
+  <si>
+    <t>0.9694,0.0449,0.0037,0.0008</t>
+  </si>
+  <si>
+    <t>0.9677,0.0335,0.0076,0.0012</t>
+  </si>
+  <si>
+    <t>0.9770,0.0224,0.0041,0.0015</t>
+  </si>
+  <si>
+    <t>0.9598,0.0504,0.0077,0.0019</t>
+  </si>
+  <si>
+    <t>0.9662,0.0370,0.0075,0.0024</t>
+  </si>
+  <si>
+    <t>0.9886,0.0154,0.0010,0.0005</t>
+  </si>
+  <si>
+    <t>0.9403,0.0650,0.0157,0.0010</t>
+  </si>
+  <si>
+    <t>0.0950,0.1771,0.8008,0.0168</t>
+  </si>
+  <si>
+    <t>0.0014,0.0027,0.9957,0.0014</t>
+  </si>
+  <si>
+    <t>0.0134,0.0352,0.9685,0.0017</t>
+  </si>
+  <si>
+    <t>0.0962,0.0094,0.9282,0.0053</t>
+  </si>
+  <si>
+    <t>0.0065,0.0010,0.9894,0.0058</t>
+  </si>
+  <si>
+    <t>0.2683,0.0236,0.7693,0.0247</t>
+  </si>
+  <si>
+    <t>0.1473,0.0029,0.8527,0.0240</t>
+  </si>
+  <si>
+    <t>0.0963,0.0248,0.8868,0.0403</t>
+  </si>
+  <si>
+    <t>0.8045,0.0093,0.0723,0.0721</t>
+  </si>
+  <si>
+    <t>0.0216,0.1110,0.0019,0.9762</t>
+  </si>
+  <si>
+    <t>0.0085,0.0025,0.0004,0.9939</t>
+  </si>
+  <si>
+    <t>0.0010,0.0009,0.0006,0.9986</t>
+  </si>
+  <si>
+    <t>0.0060,0.0014,0.0003,0.9959</t>
+  </si>
+  <si>
+    <t>0.1935,0.1704,0.0136,0.7805</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1965,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1979,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1981,10 +1990,10 @@
         <v>259</v>
       </c>
       <c r="C4" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2007,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2021,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2035,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2049,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2063,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2077,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2091,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2105,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2119,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2130,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2147,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2152,7 +2161,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2175,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2186,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2203,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2217,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2219,10 +2228,10 @@
         <v>262</v>
       </c>
       <c r="C21" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2245,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2259,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2264,7 +2273,7 @@
         <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2278,7 +2287,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2301,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2315,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2329,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2343,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2357,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2362,7 +2371,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2376,7 +2385,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2399,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2401,10 +2410,10 @@
         <v>263</v>
       </c>
       <c r="C34" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D34" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2427,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2441,7 @@
         <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2446,7 +2455,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2469,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2474,7 +2483,7 @@
         <v>263</v>
       </c>
       <c r="D39" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2497,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2511,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2525,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2539,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2553,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2567,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2578,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2595,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2609,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2623,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2637,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2651,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2665,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2679,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2693,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2707,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2721,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2735,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2749,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2763,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2777,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2791,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2805,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2819,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2833,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2847,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2852,7 +2861,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2875,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2889,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2903,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2905,10 +2914,10 @@
         <v>259</v>
       </c>
       <c r="C70" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D70" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2928,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2945,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2950,7 +2959,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2961,10 +2970,10 @@
         <v>263</v>
       </c>
       <c r="C74" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D74" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2975,10 +2984,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2992,7 +3001,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3015,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3029,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3043,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3057,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3071,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3085,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3099,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3113,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3124,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3141,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3155,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3157,10 +3166,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3183,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3197,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3211,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3225,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3239,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3253,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3267,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3281,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3295,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3309,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3323,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3337,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3351,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3365,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3379,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3393,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3407,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3421,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3435,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3449,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3463,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3477,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3491,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3493,10 +3502,10 @@
         <v>262</v>
       </c>
       <c r="C112" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3519,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3533,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3544,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3552,7 +3561,7 @@
         <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3575,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3580,7 +3589,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3600,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3605,10 +3614,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3631,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3645,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3659,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3673,7 @@
         <v>262</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3687,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3689,10 +3698,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3703,10 +3712,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3729,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3743,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3757,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3771,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3785,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3799,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3813,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3827,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3838,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3843,10 +3852,10 @@
         <v>261</v>
       </c>
       <c r="C137" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3857,10 +3866,10 @@
         <v>261</v>
       </c>
       <c r="C138" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3883,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3885,10 +3894,10 @@
         <v>259</v>
       </c>
       <c r="C140" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3911,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3916,7 +3925,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3927,10 +3936,10 @@
         <v>259</v>
       </c>
       <c r="C143" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3953,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3967,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3981,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +3995,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4009,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4023,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4025,10 +4034,10 @@
         <v>262</v>
       </c>
       <c r="C150" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4051,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4065,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4079,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4081,10 +4090,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4107,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4121,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4132,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4149,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4151,10 +4160,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4177,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4179,10 +4188,10 @@
         <v>259</v>
       </c>
       <c r="C161" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4205,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4219,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4233,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4247,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4261,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4275,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4289,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4303,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4317,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4331,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4345,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4350,7 +4359,7 @@
         <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4373,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4384,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4389,10 +4398,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4415,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4429,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4443,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4457,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4471,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4485,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4499,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4513,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4527,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4541,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4555,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4569,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4583,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4594,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4611,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4622,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4639,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4653,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4655,10 +4664,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4669,10 +4678,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4695,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4700,7 +4709,7 @@
         <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4723,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4737,7 @@
         <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4751,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4765,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4767,10 +4776,10 @@
         <v>259</v>
       </c>
       <c r="C203" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4781,10 +4790,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4798,7 +4807,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4821,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4835,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4849,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4863,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4865,10 +4874,10 @@
         <v>261</v>
       </c>
       <c r="C210" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4891,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4896,7 +4905,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4919,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4933,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4947,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4961,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4975,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4989,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5003,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5017,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5031,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5042,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5059,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5073,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5087,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5101,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5115,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5129,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5143,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5157,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5162,7 +5171,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5173,10 +5182,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5190,7 +5199,7 @@
         <v>261</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5213,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5227,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5241,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5255,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5269,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5283,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5297,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5311,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5325,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5339,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5353,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5367,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5381,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5395,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5409,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5423,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5437,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5448,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5465,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5479,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5493,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5507,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5512,7 +5521,7 @@
         <v>260</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>
